--- a/config/data/AbilityResourceDelta.xlsx
+++ b/config/data/AbilityResourceDelta.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,14 +656,14 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>20001</v>
+        <v>20002</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SkillPoints</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -678,13 +678,13 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>20002</v>
+        <v>20004</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -696,12 +696,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gain</t>
+          <t>Spend</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AbilityResolved</t>
+          <t>ActionStarted</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -712,7 +712,7 @@
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>20002</v>
+        <v>20004</v>
       </c>
       <c r="C10" t="n">
         <v>2</v>
@@ -734,20 +734,20 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>20003</v>
+        <v>20005</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SkillPoints</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -762,48 +762,48 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>20004</v>
+        <v>20006</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SkillPoints</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spend</t>
+          <t>Gain</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ActionStarted</t>
+          <t>AbilityResolved</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>20004</v>
+        <v>20007</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>SkillPoints</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -818,20 +818,20 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>20005</v>
+        <v>20007</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SkillPoints</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -846,16 +846,16 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>20005</v>
+        <v>20008</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -874,13 +874,13 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>20006</v>
+        <v>20011</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
@@ -892,12 +892,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gain</t>
+          <t>Spend</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>AbilityResolved</t>
+          <t>ActionStarted</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -908,7 +908,7 @@
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>20006</v>
+        <v>20011</v>
       </c>
       <c r="C17" t="n">
         <v>2</v>
@@ -930,13 +930,13 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>20007</v>
+        <v>20013</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -964,7 +964,7 @@
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>20007</v>
+        <v>20013</v>
       </c>
       <c r="C19" t="n">
         <v>2</v>
@@ -992,14 +992,14 @@
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>20008</v>
+        <v>20016</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SkillPoints</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1014,20 +1014,20 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>20008</v>
+        <v>20017</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>SkillPoints</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1042,20 +1042,20 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>20009</v>
+        <v>20017</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SkillPoints</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1070,20 +1070,20 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>20010</v>
+        <v>20018</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SkillPoints</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1098,13 +1098,13 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>20011</v>
+        <v>20019</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -1132,7 +1132,7 @@
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>20011</v>
+        <v>20019</v>
       </c>
       <c r="C25" t="n">
         <v>2</v>
@@ -1154,20 +1154,20 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>20012</v>
+        <v>20022</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SkillPoints</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1182,13 +1182,13 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>20013</v>
+        <v>20023</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gain</t>
+          <t>Spend</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>AbilityResolved</t>
+          <t>ActionStarted</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1216,35 +1216,35 @@
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>20013</v>
+        <v>20025</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>SkillPoints</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gain</t>
+          <t>Spend</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>AbilityResolved</t>
+          <t>ActionStarted</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>20014</v>
+        <v>20026</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
@@ -1272,14 +1272,14 @@
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>20015</v>
+        <v>20026</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SkillPoints</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1294,13 +1294,13 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>20016</v>
+        <v>20029</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gain</t>
+          <t>Spend</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>AbilityResolved</t>
+          <t>ActionStarted</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1328,7 +1328,7 @@
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>20016</v>
+        <v>20029</v>
       </c>
       <c r="C32" t="n">
         <v>2</v>
@@ -1350,20 +1350,20 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>20017</v>
+        <v>20030</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SkillPoints</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1378,20 +1378,20 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>20017</v>
+        <v>20032</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>SkillPoints</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1406,20 +1406,20 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>20018</v>
+        <v>20032</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SkillPoints</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1434,16 +1434,16 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>20018</v>
+        <v>20033</v>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>20019</v>
+        <v>20042</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spend</t>
+          <t>Gain</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>ActionStarted</t>
+          <t>AbilityResolved</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1496,923 +1496,27 @@
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>20019</v>
+        <v>20045</v>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>SkillPoints</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gain</t>
+          <t>Spend</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>AbilityResolved</t>
+          <t>ActionStarted</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="n">
-        <v>20020</v>
-      </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>SkillPoints</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="n">
-        <v>20021</v>
-      </c>
-      <c r="C40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>SkillPoints</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" t="n">
-        <v>20022</v>
-      </c>
-      <c r="C41" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>SkillPoints</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" t="n">
-        <v>20022</v>
-      </c>
-      <c r="C42" t="n">
-        <v>2</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" t="n">
-        <v>20023</v>
-      </c>
-      <c r="C43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>SkillPoints</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Spend</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>ActionStarted</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" t="n">
-        <v>20024</v>
-      </c>
-      <c r="C44" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>SkillPoints</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" t="n">
-        <v>20025</v>
-      </c>
-      <c r="C45" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>SkillPoints</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Spend</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>ActionStarted</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" t="n">
-        <v>20026</v>
-      </c>
-      <c r="C46" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>SkillPoints</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" t="n">
-        <v>20026</v>
-      </c>
-      <c r="C47" t="n">
-        <v>2</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" t="n">
-        <v>20027</v>
-      </c>
-      <c r="C48" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>SkillPoints</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" t="n">
-        <v>20028</v>
-      </c>
-      <c r="C49" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>SkillPoints</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" t="n">
-        <v>20029</v>
-      </c>
-      <c r="C50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>SkillPoints</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Spend</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>ActionStarted</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" t="n">
-        <v>20029</v>
-      </c>
-      <c r="C51" t="n">
-        <v>2</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" t="n">
-        <v>20030</v>
-      </c>
-      <c r="C52" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>SkillPoints</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" t="n">
-        <v>20030</v>
-      </c>
-      <c r="C53" t="n">
-        <v>2</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" t="n">
-        <v>20031</v>
-      </c>
-      <c r="C54" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>SkillPoints</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" t="n">
-        <v>20032</v>
-      </c>
-      <c r="C55" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>SkillPoints</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" t="n">
-        <v>20032</v>
-      </c>
-      <c r="C56" t="n">
-        <v>2</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" t="n">
-        <v>20033</v>
-      </c>
-      <c r="C57" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>SkillPoints</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" t="n">
-        <v>20033</v>
-      </c>
-      <c r="C58" t="n">
-        <v>2</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" t="n">
-        <v>20034</v>
-      </c>
-      <c r="C59" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>SkillPoints</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" t="n">
-        <v>20035</v>
-      </c>
-      <c r="C60" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>SkillPoints</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" t="n">
-        <v>20036</v>
-      </c>
-      <c r="C61" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>SkillPoints</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" t="n">
-        <v>20037</v>
-      </c>
-      <c r="C62" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>SkillPoints</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" t="n">
-        <v>20038</v>
-      </c>
-      <c r="C63" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>SkillPoints</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" t="n">
-        <v>20039</v>
-      </c>
-      <c r="C64" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>SkillPoints</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" t="n">
-        <v>20040</v>
-      </c>
-      <c r="C65" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>SkillPoints</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" t="n">
-        <v>20041</v>
-      </c>
-      <c r="C66" t="n">
-        <v>1</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>SkillPoints</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" t="n">
-        <v>20042</v>
-      </c>
-      <c r="C67" t="n">
-        <v>1</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>SkillPoints</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" t="n">
-        <v>20043</v>
-      </c>
-      <c r="C68" t="n">
-        <v>1</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>SkillPoints</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" t="n">
-        <v>20044</v>
-      </c>
-      <c r="C69" t="n">
-        <v>1</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>SkillPoints</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Gain</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>AbilityResolved</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" t="n">
-        <v>20045</v>
-      </c>
-      <c r="C70" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>SkillPoints</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Spend</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>ActionStarted</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
         <is>
           <t>1</t>
         </is>

--- a/config/data/AbilityResourceDelta.xlsx
+++ b/config/data/AbilityResourceDelta.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1522,6 +1522,1014 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>30003</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>30008</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>30010</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>30010</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>30011</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>30011</v>
+      </c>
+      <c r="C44" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>30013</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>30016</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>30019</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>30023</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>30023</v>
+      </c>
+      <c r="C49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>30024</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>30025</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>30025</v>
+      </c>
+      <c r="C52" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>30027</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>30030</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>30031</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>30031</v>
+      </c>
+      <c r="C56" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>30033</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>30035</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>30037</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>30037</v>
+      </c>
+      <c r="C60" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>30038</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>30040</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>30040</v>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>30042</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>30042</v>
+      </c>
+      <c r="C65" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>30043</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>30044</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>30045</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>30045</v>
+      </c>
+      <c r="C69" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>30048</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>30048</v>
+      </c>
+      <c r="C71" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>30049</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>30052</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>30052</v>
+      </c>
+      <c r="C74" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AbilityResourceDelta.xlsx
+++ b/config/data/AbilityResourceDelta.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2530,6 +2530,1047 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>40002</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>40003</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>40003</v>
+      </c>
+      <c r="C77" t="n">
+        <v>2</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>40006</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>40006</v>
+      </c>
+      <c r="C79" t="n">
+        <v>2</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>40008</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>40009</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>40010</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>40012</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>40012</v>
+      </c>
+      <c r="C84" t="n">
+        <v>2</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>40013</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>40016</v>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>40017</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>40019</v>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>40020</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>40020</v>
+      </c>
+      <c r="C90" t="n">
+        <v>2</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>40023</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>40023</v>
+      </c>
+      <c r="C92" t="n">
+        <v>2</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>40024</v>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>40025</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>40026</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>40026</v>
+      </c>
+      <c r="C96" t="n">
+        <v>2</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>40030</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>newbud</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>40031</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>40037</v>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="n">
+        <v>40037</v>
+      </c>
+      <c r="C100" t="n">
+        <v>2</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>40038</v>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>40038</v>
+      </c>
+      <c r="C102" t="n">
+        <v>2</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>40039</v>
+      </c>
+      <c r="C103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>40041</v>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>40041</v>
+      </c>
+      <c r="C105" t="n">
+        <v>2</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>40042</v>
+      </c>
+      <c r="C106" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>40042</v>
+      </c>
+      <c r="C107" t="n">
+        <v>2</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>40044</v>
+      </c>
+      <c r="C108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>40045</v>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>40047</v>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>40049</v>
+      </c>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AbilityResourceDelta.xlsx
+++ b/config/data/AbilityResourceDelta.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:J154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3571,6 +3571,1215 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>50002</v>
+      </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>50003</v>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>50003</v>
+      </c>
+      <c r="C114" t="n">
+        <v>2</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="n">
+        <v>50005</v>
+      </c>
+      <c r="C115" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="n">
+        <v>50005</v>
+      </c>
+      <c r="C116" t="n">
+        <v>2</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="n">
+        <v>50007</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="n">
+        <v>50007</v>
+      </c>
+      <c r="C118" t="n">
+        <v>2</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>50010</v>
+      </c>
+      <c r="C119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>50010</v>
+      </c>
+      <c r="C120" t="n">
+        <v>2</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>50011</v>
+      </c>
+      <c r="C121" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>50012</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>50012</v>
+      </c>
+      <c r="C123" t="n">
+        <v>2</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="n">
+        <v>50016</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="n">
+        <v>50016</v>
+      </c>
+      <c r="C125" t="n">
+        <v>2</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="n">
+        <v>50018</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="n">
+        <v>50018</v>
+      </c>
+      <c r="C127" t="n">
+        <v>2</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="n">
+        <v>50019</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="n">
+        <v>50019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>2</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="n">
+        <v>50020</v>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="n">
+        <v>50024</v>
+      </c>
+      <c r="C131" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="n">
+        <v>50025</v>
+      </c>
+      <c r="C132" t="n">
+        <v>1</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="n">
+        <v>50025</v>
+      </c>
+      <c r="C133" t="n">
+        <v>2</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="n">
+        <v>50026</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="n">
+        <v>50026</v>
+      </c>
+      <c r="C135" t="n">
+        <v>2</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="n">
+        <v>50028</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="n">
+        <v>50030</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="n">
+        <v>50030</v>
+      </c>
+      <c r="C138" t="n">
+        <v>2</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="n">
+        <v>50032</v>
+      </c>
+      <c r="C139" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="n">
+        <v>50033</v>
+      </c>
+      <c r="C140" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="n">
+        <v>50034</v>
+      </c>
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="n">
+        <v>50034</v>
+      </c>
+      <c r="C142" t="n">
+        <v>2</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="n">
+        <v>50037</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="n">
+        <v>50039</v>
+      </c>
+      <c r="C144" t="n">
+        <v>1</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="n">
+        <v>50040</v>
+      </c>
+      <c r="C145" t="n">
+        <v>1</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="n">
+        <v>50040</v>
+      </c>
+      <c r="C146" t="n">
+        <v>2</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="n">
+        <v>50044</v>
+      </c>
+      <c r="C147" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="n">
+        <v>50046</v>
+      </c>
+      <c r="C148" t="n">
+        <v>1</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>flying-aureus</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="n">
+        <v>50049</v>
+      </c>
+      <c r="C149" t="n">
+        <v>1</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="n">
+        <v>50052</v>
+      </c>
+      <c r="C150" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="n">
+        <v>50052</v>
+      </c>
+      <c r="C151" t="n">
+        <v>2</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="n">
+        <v>50053</v>
+      </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="n">
+        <v>50053</v>
+      </c>
+      <c r="C153" t="n">
+        <v>2</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="n">
+        <v>50055</v>
+      </c>
+      <c r="C154" t="n">
+        <v>1</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AbilityResourceDelta.xlsx
+++ b/config/data/AbilityResourceDelta.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J154"/>
+  <dimension ref="A1:J209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4780,6 +4780,1576 @@
         </is>
       </c>
     </row>
+    <row r="155">
+      <c r="B155" t="n">
+        <v>60002</v>
+      </c>
+      <c r="C155" t="n">
+        <v>1</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="n">
+        <v>60002</v>
+      </c>
+      <c r="C156" t="n">
+        <v>2</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="n">
+        <v>60005</v>
+      </c>
+      <c r="C157" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="n">
+        <v>60005</v>
+      </c>
+      <c r="C158" t="n">
+        <v>2</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="n">
+        <v>60006</v>
+      </c>
+      <c r="C159" t="n">
+        <v>1</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="n">
+        <v>60007</v>
+      </c>
+      <c r="C160" t="n">
+        <v>1</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="n">
+        <v>60007</v>
+      </c>
+      <c r="C161" t="n">
+        <v>2</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="n">
+        <v>60010</v>
+      </c>
+      <c r="C162" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="n">
+        <v>60011</v>
+      </c>
+      <c r="C163" t="n">
+        <v>1</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="n">
+        <v>60011</v>
+      </c>
+      <c r="C164" t="n">
+        <v>2</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="n">
+        <v>60012</v>
+      </c>
+      <c r="C165" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="n">
+        <v>60012</v>
+      </c>
+      <c r="C166" t="n">
+        <v>2</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="n">
+        <v>60013</v>
+      </c>
+      <c r="C167" t="n">
+        <v>1</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="n">
+        <v>60013</v>
+      </c>
+      <c r="C168" t="n">
+        <v>2</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="n">
+        <v>60017</v>
+      </c>
+      <c r="C169" t="n">
+        <v>1</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="n">
+        <v>60017</v>
+      </c>
+      <c r="C170" t="n">
+        <v>2</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="n">
+        <v>60018</v>
+      </c>
+      <c r="C171" t="n">
+        <v>1</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="n">
+        <v>60019</v>
+      </c>
+      <c r="C172" t="n">
+        <v>1</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="n">
+        <v>60019</v>
+      </c>
+      <c r="C173" t="n">
+        <v>2</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="n">
+        <v>60022</v>
+      </c>
+      <c r="C174" t="n">
+        <v>1</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="n">
+        <v>60022</v>
+      </c>
+      <c r="C175" t="n">
+        <v>2</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="n">
+        <v>60025</v>
+      </c>
+      <c r="C176" t="n">
+        <v>1</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="n">
+        <v>60025</v>
+      </c>
+      <c r="C177" t="n">
+        <v>2</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="n">
+        <v>60026</v>
+      </c>
+      <c r="C178" t="n">
+        <v>1</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="n">
+        <v>60029</v>
+      </c>
+      <c r="C179" t="n">
+        <v>1</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="n">
+        <v>60029</v>
+      </c>
+      <c r="C180" t="n">
+        <v>2</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="n">
+        <v>60030</v>
+      </c>
+      <c r="C181" t="n">
+        <v>1</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="n">
+        <v>60030</v>
+      </c>
+      <c r="C182" t="n">
+        <v>2</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="n">
+        <v>60032</v>
+      </c>
+      <c r="C183" t="n">
+        <v>1</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="n">
+        <v>60034</v>
+      </c>
+      <c r="C184" t="n">
+        <v>1</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="n">
+        <v>60036</v>
+      </c>
+      <c r="C185" t="n">
+        <v>1</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="n">
+        <v>60037</v>
+      </c>
+      <c r="C186" t="n">
+        <v>1</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="n">
+        <v>60037</v>
+      </c>
+      <c r="C187" t="n">
+        <v>2</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="n">
+        <v>60038</v>
+      </c>
+      <c r="C188" t="n">
+        <v>1</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="n">
+        <v>60038</v>
+      </c>
+      <c r="C189" t="n">
+        <v>2</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="n">
+        <v>60040</v>
+      </c>
+      <c r="C190" t="n">
+        <v>1</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>TeamResource</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>assist-use</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="n">
+        <v>60040</v>
+      </c>
+      <c r="C191" t="n">
+        <v>2</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="n">
+        <v>60041</v>
+      </c>
+      <c r="C192" t="n">
+        <v>1</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>TeamResource</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>assist-use</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="n">
+        <v>60041</v>
+      </c>
+      <c r="C193" t="n">
+        <v>2</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="n">
+        <v>60042</v>
+      </c>
+      <c r="C194" t="n">
+        <v>1</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="n">
+        <v>60042</v>
+      </c>
+      <c r="C195" t="n">
+        <v>2</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="n">
+        <v>60043</v>
+      </c>
+      <c r="C196" t="n">
+        <v>1</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>source-energy</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="n">
+        <v>60045</v>
+      </c>
+      <c r="C197" t="n">
+        <v>1</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>source-energy</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="n">
+        <v>60047</v>
+      </c>
+      <c r="C198" t="n">
+        <v>1</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>TeamResource</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>assist-use</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="n">
+        <v>60047</v>
+      </c>
+      <c r="C199" t="n">
+        <v>2</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="n">
+        <v>60048</v>
+      </c>
+      <c r="C200" t="n">
+        <v>1</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="n">
+        <v>60048</v>
+      </c>
+      <c r="C201" t="n">
+        <v>2</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>TeamResource</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>assist-use</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="n">
+        <v>60048</v>
+      </c>
+      <c r="C202" t="n">
+        <v>3</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="n">
+        <v>60049</v>
+      </c>
+      <c r="C203" t="n">
+        <v>1</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="n">
+        <v>60051</v>
+      </c>
+      <c r="C204" t="n">
+        <v>1</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="n">
+        <v>60053</v>
+      </c>
+      <c r="C205" t="n">
+        <v>1</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" t="n">
+        <v>60053</v>
+      </c>
+      <c r="C206" t="n">
+        <v>2</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="n">
+        <v>60054</v>
+      </c>
+      <c r="C207" t="n">
+        <v>1</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" t="n">
+        <v>60054</v>
+      </c>
+      <c r="C208" t="n">
+        <v>2</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" t="n">
+        <v>60055</v>
+      </c>
+      <c r="C209" t="n">
+        <v>1</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AbilityResourceDelta.xlsx
+++ b/config/data/AbilityResourceDelta.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J209"/>
+  <dimension ref="A1:J254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6350,6 +6350,1281 @@
         </is>
       </c>
     </row>
+    <row r="210">
+      <c r="B210" t="n">
+        <v>70003</v>
+      </c>
+      <c r="C210" t="n">
+        <v>1</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" t="n">
+        <v>70005</v>
+      </c>
+      <c r="C211" t="n">
+        <v>1</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" t="n">
+        <v>70005</v>
+      </c>
+      <c r="C212" t="n">
+        <v>2</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" t="n">
+        <v>70006</v>
+      </c>
+      <c r="C213" t="n">
+        <v>1</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" t="n">
+        <v>70006</v>
+      </c>
+      <c r="C214" t="n">
+        <v>2</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" t="n">
+        <v>70008</v>
+      </c>
+      <c r="C215" t="n">
+        <v>1</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" t="n">
+        <v>70008</v>
+      </c>
+      <c r="C216" t="n">
+        <v>2</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" t="n">
+        <v>70011</v>
+      </c>
+      <c r="C217" t="n">
+        <v>1</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" t="n">
+        <v>70012</v>
+      </c>
+      <c r="C218" t="n">
+        <v>1</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" t="n">
+        <v>70012</v>
+      </c>
+      <c r="C219" t="n">
+        <v>2</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" t="n">
+        <v>70016</v>
+      </c>
+      <c r="C220" t="n">
+        <v>1</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" t="n">
+        <v>70016</v>
+      </c>
+      <c r="C221" t="n">
+        <v>2</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" t="n">
+        <v>70017</v>
+      </c>
+      <c r="C222" t="n">
+        <v>1</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" t="n">
+        <v>70018</v>
+      </c>
+      <c r="C223" t="n">
+        <v>1</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" t="n">
+        <v>70018</v>
+      </c>
+      <c r="C224" t="n">
+        <v>2</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" t="n">
+        <v>70019</v>
+      </c>
+      <c r="C225" t="n">
+        <v>1</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" t="n">
+        <v>70019</v>
+      </c>
+      <c r="C226" t="n">
+        <v>2</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" t="n">
+        <v>70022</v>
+      </c>
+      <c r="C227" t="n">
+        <v>1</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" t="n">
+        <v>70023</v>
+      </c>
+      <c r="C228" t="n">
+        <v>1</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" t="n">
+        <v>70023</v>
+      </c>
+      <c r="C229" t="n">
+        <v>2</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" t="n">
+        <v>70025</v>
+      </c>
+      <c r="C230" t="n">
+        <v>1</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" t="n">
+        <v>70025</v>
+      </c>
+      <c r="C231" t="n">
+        <v>2</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" t="n">
+        <v>70027</v>
+      </c>
+      <c r="C232" t="n">
+        <v>1</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" t="n">
+        <v>70028</v>
+      </c>
+      <c r="C233" t="n">
+        <v>1</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" t="n">
+        <v>70028</v>
+      </c>
+      <c r="C234" t="n">
+        <v>2</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" t="n">
+        <v>70030</v>
+      </c>
+      <c r="C235" t="n">
+        <v>1</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" t="n">
+        <v>70033</v>
+      </c>
+      <c r="C236" t="n">
+        <v>1</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" t="n">
+        <v>70033</v>
+      </c>
+      <c r="C237" t="n">
+        <v>2</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" t="n">
+        <v>70034</v>
+      </c>
+      <c r="C238" t="n">
+        <v>1</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" t="n">
+        <v>70036</v>
+      </c>
+      <c r="C239" t="n">
+        <v>1</v>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" t="n">
+        <v>70036</v>
+      </c>
+      <c r="C240" t="n">
+        <v>2</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" t="n">
+        <v>70038</v>
+      </c>
+      <c r="C241" t="n">
+        <v>1</v>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" t="n">
+        <v>70038</v>
+      </c>
+      <c r="C242" t="n">
+        <v>2</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" t="n">
+        <v>70039</v>
+      </c>
+      <c r="C243" t="n">
+        <v>1</v>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" t="n">
+        <v>70041</v>
+      </c>
+      <c r="C244" t="n">
+        <v>1</v>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" t="n">
+        <v>70041</v>
+      </c>
+      <c r="C245" t="n">
+        <v>2</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" t="n">
+        <v>70045</v>
+      </c>
+      <c r="C246" t="n">
+        <v>1</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>syzygy</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" t="n">
+        <v>70045</v>
+      </c>
+      <c r="C247" t="n">
+        <v>2</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" t="n">
+        <v>70046</v>
+      </c>
+      <c r="C248" t="n">
+        <v>1</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" t="n">
+        <v>70046</v>
+      </c>
+      <c r="C249" t="n">
+        <v>2</v>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" t="n">
+        <v>70047</v>
+      </c>
+      <c r="C250" t="n">
+        <v>1</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>syzygy</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" t="n">
+        <v>70047</v>
+      </c>
+      <c r="C251" t="n">
+        <v>2</v>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" t="n">
+        <v>70049</v>
+      </c>
+      <c r="C252" t="n">
+        <v>1</v>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" t="n">
+        <v>70049</v>
+      </c>
+      <c r="C253" t="n">
+        <v>2</v>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>syzygy</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" t="n">
+        <v>70049</v>
+      </c>
+      <c r="C254" t="n">
+        <v>3</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AbilityResourceDelta.xlsx
+++ b/config/data/AbilityResourceDelta.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J254"/>
+  <dimension ref="A1:J312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7625,6 +7625,1695 @@
         </is>
       </c>
     </row>
+    <row r="255">
+      <c r="B255" t="n">
+        <v>80002</v>
+      </c>
+      <c r="C255" t="n">
+        <v>1</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" t="n">
+        <v>80004</v>
+      </c>
+      <c r="C256" t="n">
+        <v>1</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" t="n">
+        <v>80004</v>
+      </c>
+      <c r="C257" t="n">
+        <v>2</v>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>fuyuan-actions</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" t="n">
+        <v>80004</v>
+      </c>
+      <c r="C258" t="n">
+        <v>3</v>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" t="n">
+        <v>80005</v>
+      </c>
+      <c r="C259" t="n">
+        <v>1</v>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" t="n">
+        <v>80005</v>
+      </c>
+      <c r="C260" t="n">
+        <v>2</v>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" t="n">
+        <v>80006</v>
+      </c>
+      <c r="C261" t="n">
+        <v>1</v>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>fuyuan-actions</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" t="n">
+        <v>80007</v>
+      </c>
+      <c r="C262" t="n">
+        <v>1</v>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>fighting-will</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" t="n">
+        <v>80009</v>
+      </c>
+      <c r="C263" t="n">
+        <v>1</v>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>fighting-will</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" t="n">
+        <v>80009</v>
+      </c>
+      <c r="C264" t="n">
+        <v>2</v>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" t="n">
+        <v>80010</v>
+      </c>
+      <c r="C265" t="n">
+        <v>1</v>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" t="n">
+        <v>80010</v>
+      </c>
+      <c r="C266" t="n">
+        <v>2</v>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>fighting-will</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" t="n">
+        <v>80010</v>
+      </c>
+      <c r="C267" t="n">
+        <v>3</v>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" t="n">
+        <v>80012</v>
+      </c>
+      <c r="C268" t="n">
+        <v>1</v>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" t="n">
+        <v>80012</v>
+      </c>
+      <c r="C269" t="n">
+        <v>2</v>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>fighting-will</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" t="n">
+        <v>80012</v>
+      </c>
+      <c r="C270" t="n">
+        <v>3</v>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="B271" t="n">
+        <v>80013</v>
+      </c>
+      <c r="C271" t="n">
+        <v>1</v>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>fighting-will</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" t="n">
+        <v>80013</v>
+      </c>
+      <c r="C272" t="n">
+        <v>2</v>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" t="n">
+        <v>80016</v>
+      </c>
+      <c r="C273" t="n">
+        <v>1</v>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>abyss-flower</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" t="n">
+        <v>80016</v>
+      </c>
+      <c r="C274" t="n">
+        <v>2</v>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" t="n">
+        <v>80018</v>
+      </c>
+      <c r="C275" t="n">
+        <v>1</v>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" t="n">
+        <v>80018</v>
+      </c>
+      <c r="C276" t="n">
+        <v>2</v>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>abyss-flower</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" t="n">
+        <v>80018</v>
+      </c>
+      <c r="C277" t="n">
+        <v>3</v>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" t="n">
+        <v>80019</v>
+      </c>
+      <c r="C278" t="n">
+        <v>1</v>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" t="n">
+        <v>80019</v>
+      </c>
+      <c r="C279" t="n">
+        <v>2</v>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" t="n">
+        <v>80022</v>
+      </c>
+      <c r="C280" t="n">
+        <v>1</v>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" t="n">
+        <v>80022</v>
+      </c>
+      <c r="C281" t="n">
+        <v>2</v>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" t="n">
+        <v>80024</v>
+      </c>
+      <c r="C282" t="n">
+        <v>1</v>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="B283" t="n">
+        <v>80024</v>
+      </c>
+      <c r="C283" t="n">
+        <v>2</v>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" t="n">
+        <v>80025</v>
+      </c>
+      <c r="C284" t="n">
+        <v>1</v>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C285" t="n">
+        <v>1</v>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C286" t="n">
+        <v>2</v>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" t="n">
+        <v>80029</v>
+      </c>
+      <c r="C287" t="n">
+        <v>1</v>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" t="n">
+        <v>80030</v>
+      </c>
+      <c r="C288" t="n">
+        <v>1</v>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" t="n">
+        <v>80031</v>
+      </c>
+      <c r="C289" t="n">
+        <v>1</v>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" t="n">
+        <v>80031</v>
+      </c>
+      <c r="C290" t="n">
+        <v>2</v>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" t="n">
+        <v>80033</v>
+      </c>
+      <c r="C291" t="n">
+        <v>1</v>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>charge</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" t="n">
+        <v>80033</v>
+      </c>
+      <c r="C292" t="n">
+        <v>2</v>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" t="n">
+        <v>80035</v>
+      </c>
+      <c r="C293" t="n">
+        <v>1</v>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" t="n">
+        <v>80036</v>
+      </c>
+      <c r="C294" t="n">
+        <v>1</v>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" t="n">
+        <v>80036</v>
+      </c>
+      <c r="C295" t="n">
+        <v>2</v>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" t="n">
+        <v>80037</v>
+      </c>
+      <c r="C296" t="n">
+        <v>1</v>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" t="n">
+        <v>80038</v>
+      </c>
+      <c r="C297" t="n">
+        <v>1</v>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" t="n">
+        <v>80038</v>
+      </c>
+      <c r="C298" t="n">
+        <v>2</v>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>charge</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" t="n">
+        <v>80038</v>
+      </c>
+      <c r="C299" t="n">
+        <v>3</v>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" t="n">
+        <v>80040</v>
+      </c>
+      <c r="C300" t="n">
+        <v>1</v>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="B301" t="n">
+        <v>80040</v>
+      </c>
+      <c r="C301" t="n">
+        <v>2</v>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" t="n">
+        <v>80041</v>
+      </c>
+      <c r="C302" t="n">
+        <v>1</v>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" t="n">
+        <v>80043</v>
+      </c>
+      <c r="C303" t="n">
+        <v>1</v>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" t="n">
+        <v>80043</v>
+      </c>
+      <c r="C304" t="n">
+        <v>2</v>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>hits-per-action</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" t="n">
+        <v>80043</v>
+      </c>
+      <c r="C305" t="n">
+        <v>3</v>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" t="n">
+        <v>80044</v>
+      </c>
+      <c r="C306" t="n">
+        <v>1</v>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>hits-per-action</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" t="n">
+        <v>80045</v>
+      </c>
+      <c r="C307" t="n">
+        <v>1</v>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="B308" t="n">
+        <v>80045</v>
+      </c>
+      <c r="C308" t="n">
+        <v>2</v>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="B309" t="n">
+        <v>80046</v>
+      </c>
+      <c r="C309" t="n">
+        <v>1</v>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" t="n">
+        <v>80047</v>
+      </c>
+      <c r="C310" t="n">
+        <v>1</v>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="B311" t="n">
+        <v>80050</v>
+      </c>
+      <c r="C311" t="n">
+        <v>1</v>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" t="n">
+        <v>80052</v>
+      </c>
+      <c r="C312" t="n">
+        <v>1</v>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AbilityResourceDelta.xlsx
+++ b/config/data/AbilityResourceDelta.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J312"/>
+  <dimension ref="A1:J364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9314,6 +9314,1522 @@
         </is>
       </c>
     </row>
+    <row r="313">
+      <c r="B313" t="n">
+        <v>90003</v>
+      </c>
+      <c r="C313" t="n">
+        <v>1</v>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" t="n">
+        <v>90004</v>
+      </c>
+      <c r="C314" t="n">
+        <v>1</v>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" t="n">
+        <v>90005</v>
+      </c>
+      <c r="C315" t="n">
+        <v>1</v>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="B316" t="n">
+        <v>90005</v>
+      </c>
+      <c r="C316" t="n">
+        <v>2</v>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>charge</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="B317" t="n">
+        <v>90005</v>
+      </c>
+      <c r="C317" t="n">
+        <v>3</v>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="B318" t="n">
+        <v>90006</v>
+      </c>
+      <c r="C318" t="n">
+        <v>1</v>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" t="n">
+        <v>90006</v>
+      </c>
+      <c r="C319" t="n">
+        <v>2</v>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" t="n">
+        <v>90009</v>
+      </c>
+      <c r="C320" t="n">
+        <v>1</v>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>charge</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" t="n">
+        <v>90010</v>
+      </c>
+      <c r="C321" t="n">
+        <v>1</v>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" t="n">
+        <v>90011</v>
+      </c>
+      <c r="C322" t="n">
+        <v>1</v>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>charge</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="B323" t="n">
+        <v>90011</v>
+      </c>
+      <c r="C323" t="n">
+        <v>2</v>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" t="n">
+        <v>90012</v>
+      </c>
+      <c r="C324" t="n">
+        <v>1</v>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="B325" t="n">
+        <v>90013</v>
+      </c>
+      <c r="C325" t="n">
+        <v>1</v>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>charge</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="B326" t="n">
+        <v>90013</v>
+      </c>
+      <c r="C326" t="n">
+        <v>2</v>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="B327" t="n">
+        <v>90014</v>
+      </c>
+      <c r="C327" t="n">
+        <v>1</v>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="B328" t="n">
+        <v>90014</v>
+      </c>
+      <c r="C328" t="n">
+        <v>2</v>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="B329" t="n">
+        <v>90016</v>
+      </c>
+      <c r="C329" t="n">
+        <v>1</v>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="B330" t="n">
+        <v>90016</v>
+      </c>
+      <c r="C330" t="n">
+        <v>2</v>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="B331" t="n">
+        <v>90017</v>
+      </c>
+      <c r="C331" t="n">
+        <v>1</v>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="B332" t="n">
+        <v>90020</v>
+      </c>
+      <c r="C332" t="n">
+        <v>1</v>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="B333" t="n">
+        <v>90020</v>
+      </c>
+      <c r="C333" t="n">
+        <v>2</v>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="B334" t="n">
+        <v>90023</v>
+      </c>
+      <c r="C334" t="n">
+        <v>1</v>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="B335" t="n">
+        <v>90023</v>
+      </c>
+      <c r="C335" t="n">
+        <v>2</v>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="B336" t="n">
+        <v>90024</v>
+      </c>
+      <c r="C336" t="n">
+        <v>1</v>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="B337" t="n">
+        <v>90024</v>
+      </c>
+      <c r="C337" t="n">
+        <v>2</v>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="B338" t="n">
+        <v>90026</v>
+      </c>
+      <c r="C338" t="n">
+        <v>1</v>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="B339" t="n">
+        <v>90033</v>
+      </c>
+      <c r="C339" t="n">
+        <v>1</v>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>coreflame</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="B340" t="n">
+        <v>90034</v>
+      </c>
+      <c r="C340" t="n">
+        <v>1</v>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="B341" t="n">
+        <v>90034</v>
+      </c>
+      <c r="C341" t="n">
+        <v>2</v>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>coreflame</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="B342" t="n">
+        <v>90036</v>
+      </c>
+      <c r="C342" t="n">
+        <v>1</v>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="B343" t="n">
+        <v>90037</v>
+      </c>
+      <c r="C343" t="n">
+        <v>1</v>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>jade-tiles</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="B344" t="n">
+        <v>90037</v>
+      </c>
+      <c r="C344" t="n">
+        <v>2</v>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="B345" t="n">
+        <v>90038</v>
+      </c>
+      <c r="C345" t="n">
+        <v>1</v>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="B346" t="n">
+        <v>90038</v>
+      </c>
+      <c r="C346" t="n">
+        <v>2</v>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>jade-tiles</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="B347" t="n">
+        <v>90041</v>
+      </c>
+      <c r="C347" t="n">
+        <v>1</v>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>jade-tiles</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="B348" t="n">
+        <v>90041</v>
+      </c>
+      <c r="C348" t="n">
+        <v>2</v>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="B349" t="n">
+        <v>90042</v>
+      </c>
+      <c r="C349" t="n">
+        <v>1</v>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="B350" t="n">
+        <v>90042</v>
+      </c>
+      <c r="C350" t="n">
+        <v>2</v>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="B351" t="n">
+        <v>90043</v>
+      </c>
+      <c r="C351" t="n">
+        <v>1</v>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>jade-tiles</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="B352" t="n">
+        <v>90045</v>
+      </c>
+      <c r="C352" t="n">
+        <v>1</v>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>chroma-ink</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="B353" t="n">
+        <v>90045</v>
+      </c>
+      <c r="C353" t="n">
+        <v>2</v>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="B354" t="n">
+        <v>90046</v>
+      </c>
+      <c r="C354" t="n">
+        <v>1</v>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>chroma-ink</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="B355" t="n">
+        <v>90046</v>
+      </c>
+      <c r="C355" t="n">
+        <v>2</v>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="B356" t="n">
+        <v>90048</v>
+      </c>
+      <c r="C356" t="n">
+        <v>1</v>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="B357" t="n">
+        <v>90048</v>
+      </c>
+      <c r="C357" t="n">
+        <v>2</v>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="B358" t="n">
+        <v>90050</v>
+      </c>
+      <c r="C358" t="n">
+        <v>1</v>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="B359" t="n">
+        <v>90050</v>
+      </c>
+      <c r="C359" t="n">
+        <v>2</v>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="B360" t="n">
+        <v>90053</v>
+      </c>
+      <c r="C360" t="n">
+        <v>1</v>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="B361" t="n">
+        <v>90053</v>
+      </c>
+      <c r="C361" t="n">
+        <v>2</v>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="B362" t="n">
+        <v>90055</v>
+      </c>
+      <c r="C362" t="n">
+        <v>1</v>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="B363" t="n">
+        <v>90056</v>
+      </c>
+      <c r="C363" t="n">
+        <v>1</v>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="B364" t="n">
+        <v>90056</v>
+      </c>
+      <c r="C364" t="n">
+        <v>2</v>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AbilityResourceDelta.xlsx
+++ b/config/data/AbilityResourceDelta.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J364"/>
+  <dimension ref="A1:J408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10830,6 +10830,1248 @@
         </is>
       </c>
     </row>
+    <row r="365">
+      <c r="B365" t="n">
+        <v>100002</v>
+      </c>
+      <c r="C365" t="n">
+        <v>1</v>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="B366" t="n">
+        <v>100005</v>
+      </c>
+      <c r="C366" t="n">
+        <v>1</v>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="B367" t="n">
+        <v>100005</v>
+      </c>
+      <c r="C367" t="n">
+        <v>2</v>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="B368" t="n">
+        <v>100006</v>
+      </c>
+      <c r="C368" t="n">
+        <v>1</v>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="B369" t="n">
+        <v>100006</v>
+      </c>
+      <c r="C369" t="n">
+        <v>2</v>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="B370" t="n">
+        <v>100008</v>
+      </c>
+      <c r="C370" t="n">
+        <v>1</v>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>core-resonance</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="B371" t="n">
+        <v>100011</v>
+      </c>
+      <c r="C371" t="n">
+        <v>1</v>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="B372" t="n">
+        <v>100015</v>
+      </c>
+      <c r="C372" t="n">
+        <v>1</v>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="B373" t="n">
+        <v>100015</v>
+      </c>
+      <c r="C373" t="n">
+        <v>2</v>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="B374" t="n">
+        <v>100016</v>
+      </c>
+      <c r="C374" t="n">
+        <v>1</v>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="B375" t="n">
+        <v>100016</v>
+      </c>
+      <c r="C375" t="n">
+        <v>2</v>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="B376" t="n">
+        <v>100018</v>
+      </c>
+      <c r="C376" t="n">
+        <v>1</v>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="B377" t="n">
+        <v>100021</v>
+      </c>
+      <c r="C377" t="n">
+        <v>1</v>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="B378" t="n">
+        <v>100024</v>
+      </c>
+      <c r="C378" t="n">
+        <v>1</v>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="B379" t="n">
+        <v>100024</v>
+      </c>
+      <c r="C379" t="n">
+        <v>2</v>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="B380" t="n">
+        <v>100025</v>
+      </c>
+      <c r="C380" t="n">
+        <v>1</v>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="B381" t="n">
+        <v>100025</v>
+      </c>
+      <c r="C381" t="n">
+        <v>2</v>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="B382" t="n">
+        <v>100029</v>
+      </c>
+      <c r="C382" t="n">
+        <v>1</v>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="B383" t="n">
+        <v>100030</v>
+      </c>
+      <c r="C383" t="n">
+        <v>1</v>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="B384" t="n">
+        <v>100030</v>
+      </c>
+      <c r="C384" t="n">
+        <v>2</v>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="B385" t="n">
+        <v>100031</v>
+      </c>
+      <c r="C385" t="n">
+        <v>1</v>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="B386" t="n">
+        <v>100031</v>
+      </c>
+      <c r="C386" t="n">
+        <v>2</v>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="B387" t="n">
+        <v>100032</v>
+      </c>
+      <c r="C387" t="n">
+        <v>1</v>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="B388" t="n">
+        <v>100032</v>
+      </c>
+      <c r="C388" t="n">
+        <v>2</v>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="B389" t="n">
+        <v>100036</v>
+      </c>
+      <c r="C389" t="n">
+        <v>1</v>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="B390" t="n">
+        <v>100036</v>
+      </c>
+      <c r="C390" t="n">
+        <v>2</v>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="B391" t="n">
+        <v>100037</v>
+      </c>
+      <c r="C391" t="n">
+        <v>1</v>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="B392" t="n">
+        <v>100039</v>
+      </c>
+      <c r="C392" t="n">
+        <v>1</v>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="B393" t="n">
+        <v>100039</v>
+      </c>
+      <c r="C393" t="n">
+        <v>2</v>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="B394" t="n">
+        <v>100040</v>
+      </c>
+      <c r="C394" t="n">
+        <v>1</v>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="B395" t="n">
+        <v>100040</v>
+      </c>
+      <c r="C395" t="n">
+        <v>2</v>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="B396" t="n">
+        <v>100042</v>
+      </c>
+      <c r="C396" t="n">
+        <v>1</v>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="B397" t="n">
+        <v>100042</v>
+      </c>
+      <c r="C397" t="n">
+        <v>2</v>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="B398" t="n">
+        <v>100043</v>
+      </c>
+      <c r="C398" t="n">
+        <v>1</v>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="B399" t="n">
+        <v>100045</v>
+      </c>
+      <c r="C399" t="n">
+        <v>1</v>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="B400" t="n">
+        <v>100045</v>
+      </c>
+      <c r="C400" t="n">
+        <v>2</v>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="B401" t="n">
+        <v>100046</v>
+      </c>
+      <c r="C401" t="n">
+        <v>1</v>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="B402" t="n">
+        <v>100047</v>
+      </c>
+      <c r="C402" t="n">
+        <v>1</v>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="B403" t="n">
+        <v>100047</v>
+      </c>
+      <c r="C403" t="n">
+        <v>2</v>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="B404" t="n">
+        <v>100048</v>
+      </c>
+      <c r="C404" t="n">
+        <v>1</v>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="B405" t="n">
+        <v>100049</v>
+      </c>
+      <c r="C405" t="n">
+        <v>1</v>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="B406" t="n">
+        <v>100050</v>
+      </c>
+      <c r="C406" t="n">
+        <v>1</v>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>TeamResource</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>shared.punchline</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="B407" t="n">
+        <v>100050</v>
+      </c>
+      <c r="C407" t="n">
+        <v>2</v>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="B408" t="n">
+        <v>100051</v>
+      </c>
+      <c r="C408" t="n">
+        <v>1</v>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AbilityResourceDelta.xlsx
+++ b/config/data/AbilityResourceDelta.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J408"/>
+  <dimension ref="A1:J459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12072,6 +12072,1449 @@
         </is>
       </c>
     </row>
+    <row r="409">
+      <c r="B409" t="n">
+        <v>110002</v>
+      </c>
+      <c r="C409" t="n">
+        <v>1</v>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="B410" t="n">
+        <v>110002</v>
+      </c>
+      <c r="C410" t="n">
+        <v>2</v>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="B411" t="n">
+        <v>110003</v>
+      </c>
+      <c r="C411" t="n">
+        <v>1</v>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="B412" t="n">
+        <v>110003</v>
+      </c>
+      <c r="C412" t="n">
+        <v>2</v>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="B413" t="n">
+        <v>110004</v>
+      </c>
+      <c r="C413" t="n">
+        <v>1</v>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="B414" t="n">
+        <v>110008</v>
+      </c>
+      <c r="C414" t="n">
+        <v>1</v>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="B415" t="n">
+        <v>110008</v>
+      </c>
+      <c r="C415" t="n">
+        <v>2</v>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="B416" t="n">
+        <v>110009</v>
+      </c>
+      <c r="C416" t="n">
+        <v>1</v>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="B417" t="n">
+        <v>110009</v>
+      </c>
+      <c r="C417" t="n">
+        <v>2</v>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="B418" t="n">
+        <v>110012</v>
+      </c>
+      <c r="C418" t="n">
+        <v>1</v>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="B419" t="n">
+        <v>110014</v>
+      </c>
+      <c r="C419" t="n">
+        <v>1</v>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="B420" t="n">
+        <v>110014</v>
+      </c>
+      <c r="C420" t="n">
+        <v>2</v>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="B421" t="n">
+        <v>110015</v>
+      </c>
+      <c r="C421" t="n">
+        <v>1</v>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="B422" t="n">
+        <v>110015</v>
+      </c>
+      <c r="C422" t="n">
+        <v>2</v>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="B423" t="n">
+        <v>110017</v>
+      </c>
+      <c r="C423" t="n">
+        <v>1</v>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="B424" t="n">
+        <v>110018</v>
+      </c>
+      <c r="C424" t="n">
+        <v>1</v>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="B425" t="n">
+        <v>110020</v>
+      </c>
+      <c r="C425" t="n">
+        <v>1</v>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="B426" t="n">
+        <v>110020</v>
+      </c>
+      <c r="C426" t="n">
+        <v>2</v>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="B427" t="n">
+        <v>110021</v>
+      </c>
+      <c r="C427" t="n">
+        <v>1</v>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="B428" t="n">
+        <v>110021</v>
+      </c>
+      <c r="C428" t="n">
+        <v>2</v>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="B429" t="n">
+        <v>110022</v>
+      </c>
+      <c r="C429" t="n">
+        <v>1</v>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="B430" t="n">
+        <v>110023</v>
+      </c>
+      <c r="C430" t="n">
+        <v>1</v>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="B431" t="n">
+        <v>110023</v>
+      </c>
+      <c r="C431" t="n">
+        <v>2</v>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>inspiration</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="B432" t="n">
+        <v>110023</v>
+      </c>
+      <c r="C432" t="n">
+        <v>3</v>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="B433" t="n">
+        <v>110024</v>
+      </c>
+      <c r="C433" t="n">
+        <v>1</v>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>inspiration</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="B434" t="n">
+        <v>110024</v>
+      </c>
+      <c r="C434" t="n">
+        <v>2</v>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="B435" t="n">
+        <v>110026</v>
+      </c>
+      <c r="C435" t="n">
+        <v>1</v>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="B436" t="n">
+        <v>110028</v>
+      </c>
+      <c r="C436" t="n">
+        <v>1</v>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="B437" t="n">
+        <v>110028</v>
+      </c>
+      <c r="C437" t="n">
+        <v>2</v>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="B438" t="n">
+        <v>110029</v>
+      </c>
+      <c r="C438" t="n">
+        <v>1</v>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="B439" t="n">
+        <v>110030</v>
+      </c>
+      <c r="C439" t="n">
+        <v>1</v>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="B440" t="n">
+        <v>110030</v>
+      </c>
+      <c r="C440" t="n">
+        <v>2</v>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="B441" t="n">
+        <v>110033</v>
+      </c>
+      <c r="C441" t="n">
+        <v>1</v>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="B442" t="n">
+        <v>110033</v>
+      </c>
+      <c r="C442" t="n">
+        <v>2</v>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="B443" t="n">
+        <v>110034</v>
+      </c>
+      <c r="C443" t="n">
+        <v>1</v>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="B444" t="n">
+        <v>110034</v>
+      </c>
+      <c r="C444" t="n">
+        <v>2</v>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="B445" t="n">
+        <v>110037</v>
+      </c>
+      <c r="C445" t="n">
+        <v>1</v>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="B446" t="n">
+        <v>110039</v>
+      </c>
+      <c r="C446" t="n">
+        <v>1</v>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="B447" t="n">
+        <v>110040</v>
+      </c>
+      <c r="C447" t="n">
+        <v>1</v>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="B448" t="n">
+        <v>110041</v>
+      </c>
+      <c r="C448" t="n">
+        <v>1</v>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="B449" t="n">
+        <v>110041</v>
+      </c>
+      <c r="C449" t="n">
+        <v>2</v>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="B450" t="n">
+        <v>110044</v>
+      </c>
+      <c r="C450" t="n">
+        <v>1</v>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="B451" t="n">
+        <v>110044</v>
+      </c>
+      <c r="C451" t="n">
+        <v>2</v>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="B452" t="n">
+        <v>110045</v>
+      </c>
+      <c r="C452" t="n">
+        <v>1</v>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="B453" t="n">
+        <v>110047</v>
+      </c>
+      <c r="C453" t="n">
+        <v>1</v>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="B454" t="n">
+        <v>110048</v>
+      </c>
+      <c r="C454" t="n">
+        <v>1</v>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="B455" t="n">
+        <v>110048</v>
+      </c>
+      <c r="C455" t="n">
+        <v>2</v>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="B456" t="n">
+        <v>110049</v>
+      </c>
+      <c r="C456" t="n">
+        <v>1</v>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="B457" t="n">
+        <v>110049</v>
+      </c>
+      <c r="C457" t="n">
+        <v>2</v>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="B458" t="n">
+        <v>110050</v>
+      </c>
+      <c r="C458" t="n">
+        <v>1</v>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>TeamResource</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>shared.punchline</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="B459" t="n">
+        <v>110050</v>
+      </c>
+      <c r="C459" t="n">
+        <v>2</v>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AbilityResourceDelta.xlsx
+++ b/config/data/AbilityResourceDelta.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J459"/>
+  <dimension ref="A1:J507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13515,6 +13515,1365 @@
         </is>
       </c>
     </row>
+    <row r="460">
+      <c r="B460" t="n">
+        <v>120001</v>
+      </c>
+      <c r="C460" t="n">
+        <v>1</v>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="B461" t="n">
+        <v>120004</v>
+      </c>
+      <c r="C461" t="n">
+        <v>1</v>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="B462" t="n">
+        <v>120004</v>
+      </c>
+      <c r="C462" t="n">
+        <v>2</v>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="B463" t="n">
+        <v>120006</v>
+      </c>
+      <c r="C463" t="n">
+        <v>1</v>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="B464" t="n">
+        <v>120006</v>
+      </c>
+      <c r="C464" t="n">
+        <v>2</v>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="B465" t="n">
+        <v>120009</v>
+      </c>
+      <c r="C465" t="n">
+        <v>1</v>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="B466" t="n">
+        <v>120009</v>
+      </c>
+      <c r="C466" t="n">
+        <v>2</v>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="B467" t="n">
+        <v>120010</v>
+      </c>
+      <c r="C467" t="n">
+        <v>1</v>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="B468" t="n">
+        <v>120010</v>
+      </c>
+      <c r="C468" t="n">
+        <v>2</v>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="B469" t="n">
+        <v>120012</v>
+      </c>
+      <c r="C469" t="n">
+        <v>1</v>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="B470" t="n">
+        <v>120015</v>
+      </c>
+      <c r="C470" t="n">
+        <v>1</v>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="B471" t="n">
+        <v>120015</v>
+      </c>
+      <c r="C471" t="n">
+        <v>2</v>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="B472" t="n">
+        <v>120016</v>
+      </c>
+      <c r="C472" t="n">
+        <v>1</v>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="B473" t="n">
+        <v>120016</v>
+      </c>
+      <c r="C473" t="n">
+        <v>2</v>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="B474" t="n">
+        <v>120018</v>
+      </c>
+      <c r="C474" t="n">
+        <v>1</v>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="B475" t="n">
+        <v>120019</v>
+      </c>
+      <c r="C475" t="n">
+        <v>1</v>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="B476" t="n">
+        <v>120021</v>
+      </c>
+      <c r="C476" t="n">
+        <v>1</v>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="B477" t="n">
+        <v>120022</v>
+      </c>
+      <c r="C477" t="n">
+        <v>1</v>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="B478" t="n">
+        <v>120023</v>
+      </c>
+      <c r="C478" t="n">
+        <v>1</v>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="B479" t="n">
+        <v>120023</v>
+      </c>
+      <c r="C479" t="n">
+        <v>2</v>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="B480" t="n">
+        <v>120025</v>
+      </c>
+      <c r="C480" t="n">
+        <v>1</v>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="B481" t="n">
+        <v>120025</v>
+      </c>
+      <c r="C481" t="n">
+        <v>2</v>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="B482" t="n">
+        <v>120027</v>
+      </c>
+      <c r="C482" t="n">
+        <v>1</v>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="B483" t="n">
+        <v>120027</v>
+      </c>
+      <c r="C483" t="n">
+        <v>2</v>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="B484" t="n">
+        <v>120029</v>
+      </c>
+      <c r="C484" t="n">
+        <v>1</v>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="B485" t="n">
+        <v>120029</v>
+      </c>
+      <c r="C485" t="n">
+        <v>2</v>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="B486" t="n">
+        <v>120030</v>
+      </c>
+      <c r="C486" t="n">
+        <v>1</v>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="B487" t="n">
+        <v>120033</v>
+      </c>
+      <c r="C487" t="n">
+        <v>1</v>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="B488" t="n">
+        <v>120034</v>
+      </c>
+      <c r="C488" t="n">
+        <v>1</v>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="B489" t="n">
+        <v>120034</v>
+      </c>
+      <c r="C489" t="n">
+        <v>2</v>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="B490" t="n">
+        <v>120035</v>
+      </c>
+      <c r="C490" t="n">
+        <v>1</v>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>karma</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="B491" t="n">
+        <v>120035</v>
+      </c>
+      <c r="C491" t="n">
+        <v>2</v>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="B492" t="n">
+        <v>120036</v>
+      </c>
+      <c r="C492" t="n">
+        <v>1</v>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="B493" t="n">
+        <v>120036</v>
+      </c>
+      <c r="C493" t="n">
+        <v>2</v>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="B494" t="n">
+        <v>120038</v>
+      </c>
+      <c r="C494" t="n">
+        <v>1</v>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="B495" t="n">
+        <v>120040</v>
+      </c>
+      <c r="C495" t="n">
+        <v>1</v>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="B496" t="n">
+        <v>120040</v>
+      </c>
+      <c r="C496" t="n">
+        <v>2</v>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="B497" t="n">
+        <v>120041</v>
+      </c>
+      <c r="C497" t="n">
+        <v>1</v>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="B498" t="n">
+        <v>120041</v>
+      </c>
+      <c r="C498" t="n">
+        <v>2</v>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="B499" t="n">
+        <v>120042</v>
+      </c>
+      <c r="C499" t="n">
+        <v>1</v>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="B500" t="n">
+        <v>120045</v>
+      </c>
+      <c r="C500" t="n">
+        <v>1</v>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="B501" t="n">
+        <v>120045</v>
+      </c>
+      <c r="C501" t="n">
+        <v>2</v>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>TeamResource</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>shared.punchline</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="B502" t="n">
+        <v>120045</v>
+      </c>
+      <c r="C502" t="n">
+        <v>3</v>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="B503" t="n">
+        <v>120046</v>
+      </c>
+      <c r="C503" t="n">
+        <v>1</v>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>TeamResource</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>shared.punchline</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="B504" t="n">
+        <v>120046</v>
+      </c>
+      <c r="C504" t="n">
+        <v>2</v>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="B505" t="n">
+        <v>120047</v>
+      </c>
+      <c r="C505" t="n">
+        <v>1</v>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="B506" t="n">
+        <v>120050</v>
+      </c>
+      <c r="C506" t="n">
+        <v>1</v>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="B507" t="n">
+        <v>120050</v>
+      </c>
+      <c r="C507" t="n">
+        <v>2</v>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AbilityResourceDelta.xlsx
+++ b/config/data/AbilityResourceDelta.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J507"/>
+  <dimension ref="A1:J520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14874,6 +14874,375 @@
         </is>
       </c>
     </row>
+    <row r="508">
+      <c r="B508" t="n">
+        <v>130001</v>
+      </c>
+      <c r="C508" t="n">
+        <v>1</v>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="B509" t="n">
+        <v>130001</v>
+      </c>
+      <c r="C509" t="n">
+        <v>2</v>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="B510" t="n">
+        <v>130003</v>
+      </c>
+      <c r="C510" t="n">
+        <v>1</v>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="B511" t="n">
+        <v>130004</v>
+      </c>
+      <c r="C511" t="n">
+        <v>1</v>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="B512" t="n">
+        <v>130004</v>
+      </c>
+      <c r="C512" t="n">
+        <v>2</v>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>CharacterResource</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>roaring-bowstrings</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="B513" t="n">
+        <v>130004</v>
+      </c>
+      <c r="C513" t="n">
+        <v>3</v>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="B514" t="n">
+        <v>130008</v>
+      </c>
+      <c r="C514" t="n">
+        <v>1</v>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="B515" t="n">
+        <v>130008</v>
+      </c>
+      <c r="C515" t="n">
+        <v>2</v>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="B516" t="n">
+        <v>130009</v>
+      </c>
+      <c r="C516" t="n">
+        <v>1</v>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>ActionStarted</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="B517" t="n">
+        <v>130009</v>
+      </c>
+      <c r="C517" t="n">
+        <v>2</v>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="B518" t="n">
+        <v>130010</v>
+      </c>
+      <c r="C518" t="n">
+        <v>1</v>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="B519" t="n">
+        <v>130011</v>
+      </c>
+      <c r="C519" t="n">
+        <v>1</v>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>SkillPoints</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="B520" t="n">
+        <v>130011</v>
+      </c>
+      <c r="C520" t="n">
+        <v>2</v>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>AbilityResolved</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
